--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/16,09,26 Останкино СЫРЫ/дв 16,09,26 днрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/16,09,26 Останкино СЫРЫ/дв 16,09,26 днрсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\16,09,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87328409-2BB4-45C7-AACB-75106FEAD679}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2BF79D-3082-4DAE-86B6-AFC284992913}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -169,9 +169,6 @@
     <t>4421577 Спред растительно-сливочный "Сливочный вкус" 82,5% 180гр  Останкино</t>
   </si>
   <si>
-    <t>10,09,26 - нет на заводе / 03,09,26 - нет на заводе / 27,08,26 - нет на заводе / 24,08,26 - нет на заводе / 13,08,26 - нет на заводе / 30,07,26 - нет на заводе / 62шт в уценку (28,07,26)</t>
-  </si>
-  <si>
     <t>4421584 Спред растительно-сливочный "Сливочный вкус" 72,5% 180гр  Останкино</t>
   </si>
   <si>
@@ -327,6 +324,9 @@
   <si>
     <t>21,09,</t>
   </si>
+  <si>
+    <t>17,09,26 - нет на заводе / 10,09,26 - нет на заводе / 03,09,26 - нет на заводе / 27,08,26 - нет на заводе / 24,08,26 - нет на заводе / 13,08,26 - нет на заводе / 30,07,26 - нет на заводе / 62шт в уценку (28,07,26)</t>
+  </si>
 </sst>
 </file>
 
@@ -373,7 +373,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -393,6 +393,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -432,7 +438,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -448,6 +454,7 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -2611,13 +2618,13 @@
         <v>16</v>
       </c>
       <c r="S3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="V3" s="2" t="s">
         <v>17</v>
@@ -2705,10 +2712,10 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
@@ -2816,7 +2823,7 @@
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>3048</v>
+        <v>3024</v>
       </c>
       <c r="U5" s="4">
         <f t="shared" si="0"/>
@@ -3196,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AI8" s="1">
         <f t="shared" si="7"/>
@@ -3379,9 +3386,8 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="T10" s="5">
-        <f>VLOOKUP(A10,заказ!A:B,2,0)</f>
-        <v>12</v>
+      <c r="T10" s="15">
+        <v>0</v>
       </c>
       <c r="U10" s="13"/>
       <c r="V10" s="1" t="e">
@@ -3423,7 +3429,7 @@
         <v>0.6</v>
       </c>
       <c r="AH10" s="1" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="AI10" s="1">
         <f t="shared" si="7"/>
@@ -3448,7 +3454,7 @@
     </row>
     <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>36</v>
@@ -3489,9 +3495,8 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="T11" s="5">
-        <f>VLOOKUP(A11,заказ!A:B,2,0)</f>
-        <v>12</v>
+      <c r="T11" s="15">
+        <v>0</v>
       </c>
       <c r="U11" s="13"/>
       <c r="V11" s="1" t="e">
@@ -3533,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="1" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="AI11" s="1">
         <f t="shared" si="7"/>
@@ -3558,7 +3563,7 @@
     </row>
     <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>42</v>
@@ -3665,7 +3670,7 @@
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>36</v>
@@ -3749,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="AH13" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AI13" s="1">
         <f t="shared" si="7"/>
@@ -3774,7 +3779,7 @@
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>36</v>
@@ -3893,7 +3898,7 @@
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>36</v>
@@ -3986,7 +3991,7 @@
         <v>2.4</v>
       </c>
       <c r="AH15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AI15" s="1">
         <f>G15*S15</f>
@@ -4011,7 +4016,7 @@
     </row>
     <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>36</v>
@@ -4128,7 +4133,7 @@
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>36</v>
@@ -4221,7 +4226,7 @@
         <v>7</v>
       </c>
       <c r="AH17" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AI17" s="1">
         <f t="shared" si="7"/>
@@ -4246,7 +4251,7 @@
     </row>
     <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>36</v>
@@ -4363,7 +4368,7 @@
     </row>
     <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>36</v>
@@ -4478,7 +4483,7 @@
     </row>
     <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>36</v>
@@ -4595,7 +4600,7 @@
     </row>
     <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>36</v>
@@ -4712,7 +4717,7 @@
     </row>
     <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>36</v>
@@ -4794,7 +4799,7 @@
         <v>0.4</v>
       </c>
       <c r="AH22" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AI22" s="1">
         <f t="shared" si="7"/>
@@ -4819,7 +4824,7 @@
     </row>
     <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>36</v>
@@ -4934,7 +4939,7 @@
     </row>
     <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>36</v>
@@ -5051,7 +5056,7 @@
     </row>
     <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>36</v>
@@ -5162,7 +5167,7 @@
     </row>
     <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>36</v>
@@ -5273,7 +5278,7 @@
     </row>
     <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>36</v>
@@ -5384,7 +5389,7 @@
     </row>
     <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>36</v>
@@ -5475,7 +5480,7 @@
         <v>17.8</v>
       </c>
       <c r="AH28" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AI28" s="1">
         <f t="shared" si="7"/>
@@ -5500,7 +5505,7 @@
     </row>
     <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>36</v>
@@ -5594,7 +5599,7 @@
         <v>37</v>
       </c>
       <c r="AH29" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AI29" s="1">
         <f t="shared" si="7"/>
@@ -5619,7 +5624,7 @@
     </row>
     <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>36</v>
@@ -5705,7 +5710,7 @@
         <v>2.8</v>
       </c>
       <c r="AH30" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AI30" s="1">
         <f t="shared" si="7"/>
@@ -5730,7 +5735,7 @@
     </row>
     <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>36</v>
@@ -5818,7 +5823,7 @@
         <v>0.8</v>
       </c>
       <c r="AH31" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AI31" s="1">
         <f t="shared" si="7"/>
@@ -5843,7 +5848,7 @@
     </row>
     <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>36</v>
@@ -5960,7 +5965,7 @@
     </row>
     <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>36</v>
@@ -6048,7 +6053,7 @@
         <v>27.6</v>
       </c>
       <c r="AH33" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AI33" s="1">
         <f t="shared" si="7"/>
@@ -6073,7 +6078,7 @@
     </row>
     <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>36</v>
@@ -6185,7 +6190,7 @@
     </row>
     <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>36</v>
@@ -6302,7 +6307,7 @@
     </row>
     <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>42</v>
@@ -6417,7 +6422,7 @@
     </row>
     <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>42</v>
@@ -6503,7 +6508,7 @@
         <v>0</v>
       </c>
       <c r="AH37" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AI37" s="1">
         <f t="shared" si="7"/>
@@ -6528,7 +6533,7 @@
     </row>
     <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>42</v>
@@ -6643,7 +6648,7 @@
     </row>
     <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>42</v>
@@ -6727,7 +6732,7 @@
         <v>0.61919999999999997</v>
       </c>
       <c r="AH39" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AI39" s="1">
         <f t="shared" si="7"/>
@@ -6752,7 +6757,7 @@
     </row>
     <row r="40" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>36</v>
@@ -6871,7 +6876,7 @@
     </row>
     <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>36</v>
@@ -6988,7 +6993,7 @@
     </row>
     <row r="42" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>42</v>
@@ -7072,7 +7077,7 @@
         <v>0</v>
       </c>
       <c r="AH42" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI42" s="1">
         <f t="shared" si="7"/>
@@ -7097,7 +7102,7 @@
     </row>
     <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>36</v>
@@ -7211,7 +7216,7 @@
     </row>
     <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>36</v>
@@ -7326,7 +7331,7 @@
     </row>
     <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>42</v>
@@ -7410,7 +7415,7 @@
         <v>2.5568</v>
       </c>
       <c r="AH45" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AI45" s="1">
         <f t="shared" si="7"/>
@@ -7435,7 +7440,7 @@
     </row>
     <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>36</v>
@@ -7550,7 +7555,7 @@
     </row>
     <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>42</v>
@@ -31601,7 +31606,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4">
         <v>12</v>
@@ -31609,7 +31614,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5">
         <v>300</v>
@@ -31617,7 +31622,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6">
         <v>48</v>
@@ -31625,7 +31630,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <v>456</v>
@@ -31633,7 +31638,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>48</v>
@@ -31641,7 +31646,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B9">
         <v>48</v>
@@ -31649,7 +31654,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10">
         <v>16</v>
@@ -31657,7 +31662,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11">
         <v>350</v>
@@ -31665,7 +31670,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12">
         <v>90</v>
@@ -31673,7 +31678,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13">
         <v>28</v>
@@ -31681,7 +31686,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14">
         <v>210</v>
@@ -31689,7 +31694,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15">
         <v>20</v>
@@ -31697,7 +31702,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16">
         <v>50</v>
@@ -31705,7 +31710,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17">
         <v>400</v>
@@ -31713,7 +31718,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18">
         <v>16</v>
@@ -31721,7 +31726,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19">
         <v>64</v>
@@ -31729,7 +31734,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20">
         <v>16</v>
@@ -31737,7 +31742,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21">
         <v>50</v>
@@ -31745,7 +31750,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B22">
         <v>240</v>
@@ -31753,7 +31758,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B23">
         <v>258</v>
@@ -31761,7 +31766,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B24">
         <v>32</v>
@@ -31769,7 +31774,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B25">
         <v>60</v>
@@ -31777,7 +31782,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B26">
         <v>90</v>
@@ -31785,7 +31790,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B27">
         <v>60</v>
